--- a/output/pdf_financials_xlsx/RLYG.xlsx
+++ b/output/pdf_financials_xlsx/RLYG.xlsx
@@ -5618,31 +5618,31 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.048941</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.07706399999999999</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.008751</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.026373</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-2.90397</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-1.210522</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.676922</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.240272</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.064997</v>
       </c>
     </row>
     <row r="119">
@@ -9688,7 +9688,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RLYG.xlsx
+++ b/output/pdf_financials_xlsx/RLYG.xlsx
@@ -900,19 +900,19 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001554</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.007798</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.11209</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.100086</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.056681</v>
       </c>
     </row>
     <row r="13">
@@ -1605,19 +1605,19 @@
         <v>-0.122253</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.075532</v>
+        <v>-1.077086</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.20837</v>
+        <v>1.200572</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.65877</v>
+        <v>-0.77086</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.966961</v>
+        <v>-1.067047</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.756334</v>
+        <v>-4.813015</v>
       </c>
     </row>
     <row r="28">
@@ -1691,19 +1691,19 @@
         <v>-0.122253</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.075532</v>
+        <v>-1.077086</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.20837</v>
+        <v>1.200572</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.65877</v>
+        <v>-0.77086</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.966961</v>
+        <v>-1.067047</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.756334</v>
+        <v>-4.813015</v>
       </c>
     </row>
     <row r="30">
@@ -1897,40 +1897,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.24308</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.3291</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.245916</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.375976</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.304394</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.170049</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.027995</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.255386</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.964296</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.224246</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.402218</v>
       </c>
     </row>
     <row r="35">
@@ -1983,40 +1983,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.24308</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.3291</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.245916</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.375976</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.304394</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.170049</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.027995</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.255386</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.964296</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.224246</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.402218</v>
       </c>
     </row>
     <row r="37">
@@ -2499,40 +2499,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.312163</v>
+        <v>0.06908300000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.33084</v>
+        <v>0.00174</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.248479</v>
+        <v>0.002563</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.385153</v>
+        <v>0.009176999999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.313607</v>
+        <v>0.009213000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.180711</v>
+        <v>0.010662</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.171342</v>
+        <v>0.143347</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.276331</v>
+        <v>0.020945</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.988256</v>
+        <v>0.02396</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.248527</v>
+        <v>0.024281</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.429808</v>
+        <v>0.02759</v>
       </c>
     </row>
     <row r="49">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">

--- a/output/pdf_financials_xlsx/RLYG.xlsx
+++ b/output/pdf_financials_xlsx/RLYG.xlsx
@@ -5335,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012389</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -6380,7 +6380,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012389</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>-0.296189</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.472103</v>
+        <v>-0.484492</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-1.001096</v>
@@ -10608,7 +10608,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -11398,7 +11402,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -12540,7 +12548,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>-0.000443</v>
       </c>
